--- a/simulation/B型_愛媛_開設シミュレーション.xlsx
+++ b/simulation/B型_愛媛_開設シミュレーション.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="215">
   <si>
     <r>
       <rPr>
@@ -2848,7 +2848,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">第三管理部、地域共創課</t>
+    <t xml:space="preserve">第三管理部 事業開発課 地域共創係</t>
   </si>
   <si>
     <r>
@@ -2916,7 +2916,7 @@
     <t xml:space="preserve">放デイ（日吉・西条）の中高生の人数と卒業時期、保護者アンケート。特別支援学校の進路担当・相談支援事業所へのヒアリング。</t>
   </si>
   <si>
-    <t xml:space="preserve">相談支援、放デイ各事業所</t>
+    <t xml:space="preserve">第三管理部 マーケティング課 トータルサポート推進係、相談支援、放デイ各事業所</t>
   </si>
   <si>
     <r>
@@ -2965,9 +2965,6 @@
     <t xml:space="preserve">本シミュレーションを実数に置き換え、投資額・回収計画を役員へ提示。</t>
   </si>
   <si>
-    <t xml:space="preserve">第三管理部</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3014,9 +3011,6 @@
     <t xml:space="preserve">送迎しやすい立地、作業スペース、用途・消防の適合を確認。</t>
   </si>
   <si>
-    <t xml:space="preserve">地域共創課</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3082,7 +3076,7 @@
     <t xml:space="preserve">地域企業の軽作業、農福連携（西条の農業）、飲食・製菓など、平均工賃を上げられる作業を確保。</t>
   </si>
   <si>
-    <t xml:space="preserve">ラトリエトゥボナペティ、ソーシャルカレッジリッツ、地域共創課</t>
+    <t xml:space="preserve">第三管理部 事業開発課 地域共創係、ラトリエトゥボナペティ ほか</t>
   </si>
   <si>
     <r>
@@ -3245,7 +3239,7 @@
     <t xml:space="preserve">放デイ卒業生・特別支援学校卒業生の受け入れ。初年度は利用者の確保と工賃の底上げに集中。</t>
   </si>
   <si>
-    <t xml:space="preserve">全事業部</t>
+    <t xml:space="preserve">第三管理部 マーケティング課 トータルサポート推進係（利用者・保護者への周知）</t>
   </si>
   <si>
     <r>
@@ -10142,91 +10136,91 @@
         <v>192</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="C7" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>196</v>
-      </c>
       <c r="D7" s="43" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="D8" s="43" t="s">
         <v>199</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>202</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="D9" s="43" t="s">
         <v>203</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>208</v>
-      </c>
       <c r="D10" s="43" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="D11" s="43" t="s">
         <v>210</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="43" t="s">
         <v>213</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="D12" s="43" t="s">
         <v>214</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>
